--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.71697063291865</v>
+        <v>9.70400772784928</v>
       </c>
       <c r="D2" t="n">
-        <v>58.45470667721497</v>
+        <v>9.498889835047434</v>
       </c>
       <c r="E2" t="n">
-        <v>10.03534293448899</v>
+        <v>1.630743226854461</v>
       </c>
       <c r="F2" t="n">
-        <v>15.09583936112222</v>
+        <v>2.453073896182361</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>84.74016652531523</v>
+        <v>13.77027706036372</v>
       </c>
       <c r="D3" t="n">
-        <v>83.85840398880383</v>
+        <v>13.62699064818062</v>
       </c>
       <c r="E3" t="n">
-        <v>10.03534293448899</v>
+        <v>1.630743226854461</v>
       </c>
       <c r="F3" t="n">
-        <v>15.09583936112222</v>
+        <v>2.453073896182361</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>80.63114896597027</v>
+        <v>13.10256170697017</v>
       </c>
       <c r="D4" t="n">
-        <v>80.1150594318235</v>
+        <v>13.01869715767132</v>
       </c>
       <c r="E4" t="n">
-        <v>10.03534293448899</v>
+        <v>1.630743226854461</v>
       </c>
       <c r="F4" t="n">
-        <v>15.09583936112222</v>
+        <v>2.453073896182361</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>83.11078305456431</v>
+        <v>13.5055022463667</v>
       </c>
       <c r="D5" t="n">
-        <v>79.8990417923787</v>
+        <v>12.98359429126154</v>
       </c>
       <c r="E5" t="n">
-        <v>10.03534293448899</v>
+        <v>1.630743226854461</v>
       </c>
       <c r="F5" t="n">
-        <v>15.09583936112222</v>
+        <v>2.453073896182361</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>66.18639696693181</v>
+        <v>10.75528950712642</v>
       </c>
       <c r="D6" t="n">
-        <v>45.20102547593904</v>
+        <v>7.345166639840095</v>
       </c>
       <c r="E6" t="n">
-        <v>10.03534293448899</v>
+        <v>1.630743226854461</v>
       </c>
       <c r="F6" t="n">
-        <v>15.09583936112222</v>
+        <v>2.453073896182361</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
